--- a/AAII_Financials/Yearly/NSRGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NSRGY_YR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -709,16 +709,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>105225400</v>
+        <v>104012700</v>
       </c>
       <c r="E8" s="3">
-        <v>106838900</v>
+        <v>105607600</v>
       </c>
       <c r="F8" s="3">
-        <v>98538300</v>
+        <v>97402700</v>
       </c>
       <c r="G8" s="3">
-        <v>95432400</v>
+        <v>94332600</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -736,16 +736,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>56945100</v>
+        <v>56288800</v>
       </c>
       <c r="E9" s="3">
-        <v>58548400</v>
+        <v>57873700</v>
       </c>
       <c r="F9" s="3">
-        <v>51446100</v>
+        <v>50853200</v>
       </c>
       <c r="G9" s="3">
-        <v>48620800</v>
+        <v>48060500</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -763,16 +763,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>48280300</v>
+        <v>47723800</v>
       </c>
       <c r="E10" s="3">
-        <v>48290400</v>
+        <v>47733900</v>
       </c>
       <c r="F10" s="3">
-        <v>47092200</v>
+        <v>46549500</v>
       </c>
       <c r="G10" s="3">
-        <v>46811600</v>
+        <v>46272100</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -803,16 +803,16 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1873700</v>
+        <v>1852100</v>
       </c>
       <c r="E12" s="3">
-        <v>1919000</v>
+        <v>1896900</v>
       </c>
       <c r="F12" s="3">
-        <v>1889600</v>
+        <v>1867800</v>
       </c>
       <c r="G12" s="3">
-        <v>1783200</v>
+        <v>1762700</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -857,16 +857,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1819400</v>
+        <v>1798500</v>
       </c>
       <c r="E14" s="3">
-        <v>3781400</v>
+        <v>3737800</v>
       </c>
       <c r="F14" s="3">
-        <v>3791600</v>
+        <v>3747900</v>
       </c>
       <c r="G14" s="3">
-        <v>-574800</v>
+        <v>-568200</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -921,16 +921,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>89313400</v>
+        <v>88284100</v>
       </c>
       <c r="E17" s="3">
-        <v>92892200</v>
+        <v>91821700</v>
       </c>
       <c r="F17" s="3">
-        <v>85323800</v>
+        <v>84340400</v>
       </c>
       <c r="G17" s="3">
-        <v>78691000</v>
+        <v>77784100</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -948,16 +948,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>15912000</v>
+        <v>15728600</v>
       </c>
       <c r="E18" s="3">
-        <v>13946600</v>
+        <v>13785900</v>
       </c>
       <c r="F18" s="3">
-        <v>13214600</v>
+        <v>13062300</v>
       </c>
       <c r="G18" s="3">
-        <v>16741400</v>
+        <v>16548400</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -988,16 +988,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>158400</v>
+        <v>156600</v>
       </c>
       <c r="E20" s="3">
-        <v>95000</v>
+        <v>93900</v>
       </c>
       <c r="F20" s="3">
-        <v>-65600</v>
+        <v>-64900</v>
       </c>
       <c r="G20" s="3">
-        <v>-48700</v>
+        <v>-48100</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1015,16 +1015,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>20005800</v>
+        <v>19738600</v>
       </c>
       <c r="E21" s="3">
-        <v>18071500</v>
+        <v>17825700</v>
       </c>
       <c r="F21" s="3">
-        <v>17063800</v>
+        <v>16830700</v>
       </c>
       <c r="G21" s="3">
-        <v>20636000</v>
+        <v>20361500</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1042,16 +1042,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1697200</v>
+        <v>1677700</v>
       </c>
       <c r="E22" s="3">
-        <v>1271800</v>
+        <v>1257100</v>
       </c>
       <c r="F22" s="3">
-        <v>922200</v>
+        <v>911500</v>
       </c>
       <c r="G22" s="3">
-        <v>940300</v>
+        <v>929400</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1069,16 +1069,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>14373200</v>
+        <v>14207500</v>
       </c>
       <c r="E23" s="3">
-        <v>12769900</v>
+        <v>12622700</v>
       </c>
       <c r="F23" s="3">
-        <v>12226800</v>
+        <v>12085900</v>
       </c>
       <c r="G23" s="3">
-        <v>15752500</v>
+        <v>15570900</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1096,16 +1096,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2618200</v>
+        <v>2588100</v>
       </c>
       <c r="E24" s="3">
-        <v>3088900</v>
+        <v>3053300</v>
       </c>
       <c r="F24" s="3">
-        <v>2558300</v>
+        <v>2528800</v>
       </c>
       <c r="G24" s="3">
-        <v>3807400</v>
+        <v>3763600</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1150,16 +1150,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>11754900</v>
+        <v>11619500</v>
       </c>
       <c r="E26" s="3">
-        <v>9680900</v>
+        <v>9569400</v>
       </c>
       <c r="F26" s="3">
-        <v>9668500</v>
+        <v>9557100</v>
       </c>
       <c r="G26" s="3">
-        <v>11945000</v>
+        <v>11807400</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1177,16 +1177,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>12682800</v>
+        <v>12536600</v>
       </c>
       <c r="E27" s="3">
-        <v>10488800</v>
+        <v>10367900</v>
       </c>
       <c r="F27" s="3">
-        <v>19127700</v>
+        <v>18907200</v>
       </c>
       <c r="G27" s="3">
-        <v>13840300</v>
+        <v>13680800</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-158400</v>
+        <v>-156600</v>
       </c>
       <c r="E32" s="3">
-        <v>-95000</v>
+        <v>-93900</v>
       </c>
       <c r="F32" s="3">
-        <v>65600</v>
+        <v>64900</v>
       </c>
       <c r="G32" s="3">
-        <v>48700</v>
+        <v>48100</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1339,16 +1339,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>12682800</v>
+        <v>12536600</v>
       </c>
       <c r="E33" s="3">
-        <v>10488800</v>
+        <v>10367900</v>
       </c>
       <c r="F33" s="3">
-        <v>19127700</v>
+        <v>18907200</v>
       </c>
       <c r="G33" s="3">
-        <v>13840300</v>
+        <v>13680800</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1393,16 +1393,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>12682800</v>
+        <v>12536600</v>
       </c>
       <c r="E35" s="3">
-        <v>10488800</v>
+        <v>10367900</v>
       </c>
       <c r="F35" s="3">
-        <v>19127700</v>
+        <v>18907200</v>
       </c>
       <c r="G35" s="3">
-        <v>13840300</v>
+        <v>13680800</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1478,16 +1478,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5449200</v>
+        <v>5386400</v>
       </c>
       <c r="E41" s="3">
-        <v>6235600</v>
+        <v>6163700</v>
       </c>
       <c r="F41" s="3">
-        <v>7906800</v>
+        <v>7815700</v>
       </c>
       <c r="G41" s="3">
-        <v>5923300</v>
+        <v>5855000</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1505,16 +1505,16 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1171100</v>
+        <v>1157600</v>
       </c>
       <c r="E42" s="3">
-        <v>1330600</v>
+        <v>1315300</v>
       </c>
       <c r="F42" s="3">
-        <v>7928300</v>
+        <v>7836900</v>
       </c>
       <c r="G42" s="3">
-        <v>3817600</v>
+        <v>3773600</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1532,16 +1532,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13893400</v>
+        <v>13733300</v>
       </c>
       <c r="E43" s="3">
-        <v>14031500</v>
+        <v>13869800</v>
       </c>
       <c r="F43" s="3">
-        <v>13984000</v>
+        <v>13822800</v>
       </c>
       <c r="G43" s="3">
-        <v>12960000</v>
+        <v>12810600</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1559,16 +1559,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>13460100</v>
+        <v>13305000</v>
       </c>
       <c r="E44" s="3">
-        <v>16993700</v>
+        <v>16797900</v>
       </c>
       <c r="F44" s="3">
-        <v>13557400</v>
+        <v>13401100</v>
       </c>
       <c r="G44" s="3">
-        <v>11429100</v>
+        <v>11297400</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1586,16 +1586,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>940300</v>
+        <v>929400</v>
       </c>
       <c r="E45" s="3">
-        <v>1080600</v>
+        <v>1068100</v>
       </c>
       <c r="F45" s="3">
-        <v>1042100</v>
+        <v>1030100</v>
       </c>
       <c r="G45" s="3">
-        <v>4417300</v>
+        <v>4366400</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1613,16 +1613,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>34914100</v>
+        <v>34511700</v>
       </c>
       <c r="E46" s="3">
-        <v>39672000</v>
+        <v>39214700</v>
       </c>
       <c r="F46" s="3">
-        <v>44418500</v>
+        <v>43906600</v>
       </c>
       <c r="G46" s="3">
-        <v>38547300</v>
+        <v>38103000</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1640,16 +1640,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>18143300</v>
+        <v>17934200</v>
       </c>
       <c r="E47" s="3">
-        <v>18416000</v>
+        <v>18203700</v>
       </c>
       <c r="F47" s="3">
-        <v>16553600</v>
+        <v>16362800</v>
       </c>
       <c r="G47" s="3">
-        <v>16518500</v>
+        <v>16328100</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1667,16 +1667,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34472800</v>
+        <v>34075500</v>
       </c>
       <c r="E48" s="3">
-        <v>34103900</v>
+        <v>33710900</v>
       </c>
       <c r="F48" s="3">
-        <v>32071800</v>
+        <v>31702200</v>
       </c>
       <c r="G48" s="3">
-        <v>29237400</v>
+        <v>28900500</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1694,16 +1694,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>53086800</v>
+        <v>52475000</v>
       </c>
       <c r="E49" s="3">
-        <v>58270100</v>
+        <v>57598500</v>
       </c>
       <c r="F49" s="3">
-        <v>60234300</v>
+        <v>59540200</v>
       </c>
       <c r="G49" s="3">
-        <v>54048500</v>
+        <v>53425600</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1775,16 +1775,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2571900</v>
+        <v>2542200</v>
       </c>
       <c r="E52" s="3">
-        <v>2493800</v>
+        <v>2465000</v>
       </c>
       <c r="F52" s="3">
-        <v>4158200</v>
+        <v>4110300</v>
       </c>
       <c r="G52" s="3">
-        <v>1983500</v>
+        <v>1960600</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1829,16 +1829,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>143189000</v>
+        <v>141539000</v>
       </c>
       <c r="E54" s="3">
-        <v>152956000</v>
+        <v>151193000</v>
       </c>
       <c r="F54" s="3">
-        <v>157436000</v>
+        <v>155622000</v>
       </c>
       <c r="G54" s="3">
-        <v>140335000</v>
+        <v>138718000</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -1882,16 +1882,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>16061400</v>
+        <v>15876300</v>
       </c>
       <c r="E57" s="3">
-        <v>17875100</v>
+        <v>17669100</v>
       </c>
       <c r="F57" s="3">
-        <v>17679400</v>
+        <v>17475600</v>
       </c>
       <c r="G57" s="3">
-        <v>15616700</v>
+        <v>15436700</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -1909,16 +1909,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10654000</v>
+        <v>10531200</v>
       </c>
       <c r="E58" s="3">
-        <v>12324100</v>
+        <v>12182000</v>
       </c>
       <c r="F58" s="3">
-        <v>11418900</v>
+        <v>11287300</v>
       </c>
       <c r="G58" s="3">
-        <v>13599300</v>
+        <v>13442500</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -1936,16 +1936,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15244400</v>
+        <v>15068700</v>
       </c>
       <c r="E59" s="3">
-        <v>15032800</v>
+        <v>14859600</v>
       </c>
       <c r="F59" s="3">
-        <v>16183600</v>
+        <v>15997000</v>
       </c>
       <c r="G59" s="3">
-        <v>15728700</v>
+        <v>15547400</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -1963,16 +1963,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>41959800</v>
+        <v>41476200</v>
       </c>
       <c r="E60" s="3">
-        <v>45232000</v>
+        <v>44710800</v>
       </c>
       <c r="F60" s="3">
-        <v>45281800</v>
+        <v>44760000</v>
       </c>
       <c r="G60" s="3">
-        <v>44944600</v>
+        <v>44426700</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -1990,16 +1990,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>51850100</v>
+        <v>51252500</v>
       </c>
       <c r="E61" s="3">
-        <v>49128900</v>
+        <v>48562700</v>
       </c>
       <c r="F61" s="3">
-        <v>41278700</v>
+        <v>40802900</v>
       </c>
       <c r="G61" s="3">
-        <v>31600000</v>
+        <v>31235800</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2017,16 +2017,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8207800</v>
+        <v>8113200</v>
       </c>
       <c r="E62" s="3">
-        <v>10176500</v>
+        <v>10059200</v>
       </c>
       <c r="F62" s="3">
-        <v>10084900</v>
+        <v>9968700</v>
       </c>
       <c r="G62" s="3">
-        <v>11160900</v>
+        <v>11032300</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2125,16 +2125,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>102747000</v>
+        <v>101563000</v>
       </c>
       <c r="E66" s="3">
-        <v>105454000</v>
+        <v>104239000</v>
       </c>
       <c r="F66" s="3">
-        <v>97309500</v>
+        <v>96188100</v>
       </c>
       <c r="G66" s="3">
-        <v>88632200</v>
+        <v>87610800</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2273,16 +2273,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>76954200</v>
+        <v>76067300</v>
       </c>
       <c r="E72" s="3">
-        <v>84385800</v>
+        <v>83413300</v>
       </c>
       <c r="F72" s="3">
-        <v>91812800</v>
+        <v>90754700</v>
       </c>
       <c r="G72" s="3">
-        <v>86479000</v>
+        <v>85482400</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2381,16 +2381,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>40441400</v>
+        <v>39975300</v>
       </c>
       <c r="E76" s="3">
-        <v>47501800</v>
+        <v>46954300</v>
       </c>
       <c r="F76" s="3">
-        <v>60126800</v>
+        <v>59433900</v>
       </c>
       <c r="G76" s="3">
-        <v>51703000</v>
+        <v>51107100</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2467,16 +2467,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>12682800</v>
+        <v>12536600</v>
       </c>
       <c r="E81" s="3">
-        <v>10488800</v>
+        <v>10367900</v>
       </c>
       <c r="F81" s="3">
-        <v>19127700</v>
+        <v>18907200</v>
       </c>
       <c r="G81" s="3">
-        <v>13840300</v>
+        <v>13680800</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2507,16 +2507,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3912700</v>
+        <v>3867600</v>
       </c>
       <c r="E83" s="3">
-        <v>4006600</v>
+        <v>3960400</v>
       </c>
       <c r="F83" s="3">
-        <v>3892300</v>
+        <v>3847400</v>
       </c>
       <c r="G83" s="3">
-        <v>3920600</v>
+        <v>3875400</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2669,16 +2669,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>18036900</v>
+        <v>17829100</v>
       </c>
       <c r="E89" s="3">
-        <v>13472500</v>
+        <v>13317300</v>
       </c>
       <c r="F89" s="3">
-        <v>15686800</v>
+        <v>15506100</v>
       </c>
       <c r="G89" s="3">
-        <v>16267300</v>
+        <v>16079800</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2709,16 +2709,16 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6465300</v>
+        <v>-6390800</v>
       </c>
       <c r="E91" s="3">
-        <v>-5764900</v>
+        <v>-5698500</v>
       </c>
       <c r="F91" s="3">
-        <v>-5521600</v>
+        <v>-5458000</v>
       </c>
       <c r="G91" s="3">
-        <v>-4611900</v>
+        <v>-4558800</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -2790,16 +2790,16 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-7010700</v>
+        <v>-6929900</v>
       </c>
       <c r="E94" s="3">
-        <v>-2153200</v>
+        <v>-2128400</v>
       </c>
       <c r="F94" s="3">
-        <v>-3444200</v>
+        <v>-3404500</v>
       </c>
       <c r="G94" s="3">
-        <v>-6412100</v>
+        <v>-6338200</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -2830,16 +2830,16 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8858400</v>
+        <v>-8756300</v>
       </c>
       <c r="E96" s="3">
-        <v>-8619600</v>
+        <v>-8520300</v>
       </c>
       <c r="F96" s="3">
-        <v>-8690900</v>
+        <v>-8590700</v>
       </c>
       <c r="G96" s="3">
-        <v>-8712400</v>
+        <v>-8612000</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -2938,16 +2938,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-11041000</v>
+        <v>-10913700</v>
       </c>
       <c r="E100" s="3">
-        <v>-12881900</v>
+        <v>-12733400</v>
       </c>
       <c r="F100" s="3">
-        <v>-10355300</v>
+        <v>-10236000</v>
       </c>
       <c r="G100" s="3">
-        <v>-11747000</v>
+        <v>-11611600</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -2965,16 +2965,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-771700</v>
+        <v>-762800</v>
       </c>
       <c r="E101" s="3">
-        <v>-113100</v>
+        <v>-111800</v>
       </c>
       <c r="F101" s="3">
-        <v>100700</v>
+        <v>99500</v>
       </c>
       <c r="G101" s="3">
-        <v>-635900</v>
+        <v>-628600</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -2992,16 +2992,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-786400</v>
+        <v>-777300</v>
       </c>
       <c r="E102" s="3">
-        <v>-1675700</v>
+        <v>-1656400</v>
       </c>
       <c r="F102" s="3">
-        <v>1988000</v>
+        <v>1965100</v>
       </c>
       <c r="G102" s="3">
-        <v>-2527700</v>
+        <v>-2498600</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/NSRGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NSRGY_YR_FIN.xlsx
@@ -709,16 +709,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>104012700</v>
+        <v>109551600</v>
       </c>
       <c r="E8" s="3">
-        <v>105607600</v>
+        <v>111231500</v>
       </c>
       <c r="F8" s="3">
-        <v>97402700</v>
+        <v>102589700</v>
       </c>
       <c r="G8" s="3">
-        <v>94332600</v>
+        <v>99356100</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -736,16 +736,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>56288800</v>
+        <v>59286400</v>
       </c>
       <c r="E9" s="3">
-        <v>57873700</v>
+        <v>60955600</v>
       </c>
       <c r="F9" s="3">
-        <v>50853200</v>
+        <v>53561300</v>
       </c>
       <c r="G9" s="3">
-        <v>48060500</v>
+        <v>50619800</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -763,16 +763,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>47723800</v>
+        <v>50265300</v>
       </c>
       <c r="E10" s="3">
-        <v>47733900</v>
+        <v>50275900</v>
       </c>
       <c r="F10" s="3">
-        <v>46549500</v>
+        <v>49028400</v>
       </c>
       <c r="G10" s="3">
-        <v>46272100</v>
+        <v>48736200</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -803,16 +803,16 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1852100</v>
+        <v>1950800</v>
       </c>
       <c r="E12" s="3">
-        <v>1896900</v>
+        <v>1997900</v>
       </c>
       <c r="F12" s="3">
-        <v>1867800</v>
+        <v>1967300</v>
       </c>
       <c r="G12" s="3">
-        <v>1762700</v>
+        <v>1856500</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -857,16 +857,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1798500</v>
+        <v>1894200</v>
       </c>
       <c r="E14" s="3">
-        <v>3737800</v>
+        <v>3936900</v>
       </c>
       <c r="F14" s="3">
-        <v>3747900</v>
+        <v>3947500</v>
       </c>
       <c r="G14" s="3">
-        <v>-568200</v>
+        <v>-598400</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -921,16 +921,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>88284100</v>
+        <v>92985400</v>
       </c>
       <c r="E17" s="3">
-        <v>91821700</v>
+        <v>96711400</v>
       </c>
       <c r="F17" s="3">
-        <v>84340400</v>
+        <v>88831800</v>
       </c>
       <c r="G17" s="3">
-        <v>77784100</v>
+        <v>81926400</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -948,16 +948,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>15728600</v>
+        <v>16566200</v>
       </c>
       <c r="E18" s="3">
-        <v>13785900</v>
+        <v>14520000</v>
       </c>
       <c r="F18" s="3">
-        <v>13062300</v>
+        <v>13757900</v>
       </c>
       <c r="G18" s="3">
-        <v>16548400</v>
+        <v>17429700</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -988,16 +988,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>156600</v>
+        <v>164900</v>
       </c>
       <c r="E20" s="3">
-        <v>93900</v>
+        <v>99000</v>
       </c>
       <c r="F20" s="3">
-        <v>-64900</v>
+        <v>-68300</v>
       </c>
       <c r="G20" s="3">
-        <v>-48100</v>
+        <v>-50700</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1015,16 +1015,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>19738600</v>
+        <v>20794600</v>
       </c>
       <c r="E21" s="3">
-        <v>17825700</v>
+        <v>18780000</v>
       </c>
       <c r="F21" s="3">
-        <v>16830700</v>
+        <v>17731800</v>
       </c>
       <c r="G21" s="3">
-        <v>20361500</v>
+        <v>21450700</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1042,16 +1042,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1677700</v>
+        <v>1767000</v>
       </c>
       <c r="E22" s="3">
-        <v>1257100</v>
+        <v>1324100</v>
       </c>
       <c r="F22" s="3">
-        <v>911500</v>
+        <v>960100</v>
       </c>
       <c r="G22" s="3">
-        <v>929400</v>
+        <v>978900</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1069,16 +1069,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>14207500</v>
+        <v>14964100</v>
       </c>
       <c r="E23" s="3">
-        <v>12622700</v>
+        <v>13294900</v>
       </c>
       <c r="F23" s="3">
-        <v>12085900</v>
+        <v>12729500</v>
       </c>
       <c r="G23" s="3">
-        <v>15570900</v>
+        <v>16400100</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1096,16 +1096,16 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2588100</v>
+        <v>2725900</v>
       </c>
       <c r="E24" s="3">
-        <v>3053300</v>
+        <v>3215900</v>
       </c>
       <c r="F24" s="3">
-        <v>2528800</v>
+        <v>2663500</v>
       </c>
       <c r="G24" s="3">
-        <v>3763600</v>
+        <v>3964000</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1150,16 +1150,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>11619500</v>
+        <v>12238200</v>
       </c>
       <c r="E26" s="3">
-        <v>9569400</v>
+        <v>10079000</v>
       </c>
       <c r="F26" s="3">
-        <v>9557100</v>
+        <v>10066000</v>
       </c>
       <c r="G26" s="3">
-        <v>11807400</v>
+        <v>12436100</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1177,16 +1177,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>12536600</v>
+        <v>13204200</v>
       </c>
       <c r="E27" s="3">
-        <v>10367900</v>
+        <v>10920100</v>
       </c>
       <c r="F27" s="3">
-        <v>18907200</v>
+        <v>19914100</v>
       </c>
       <c r="G27" s="3">
-        <v>13680800</v>
+        <v>14409300</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-156600</v>
+        <v>-164900</v>
       </c>
       <c r="E32" s="3">
-        <v>-93900</v>
+        <v>-99000</v>
       </c>
       <c r="F32" s="3">
-        <v>64900</v>
+        <v>68300</v>
       </c>
       <c r="G32" s="3">
-        <v>48100</v>
+        <v>50700</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1339,16 +1339,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>12536600</v>
+        <v>13204200</v>
       </c>
       <c r="E33" s="3">
-        <v>10367900</v>
+        <v>10920100</v>
       </c>
       <c r="F33" s="3">
-        <v>18907200</v>
+        <v>19914100</v>
       </c>
       <c r="G33" s="3">
-        <v>13680800</v>
+        <v>14409300</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1393,16 +1393,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>12536600</v>
+        <v>13204200</v>
       </c>
       <c r="E35" s="3">
-        <v>10367900</v>
+        <v>10920100</v>
       </c>
       <c r="F35" s="3">
-        <v>18907200</v>
+        <v>19914100</v>
       </c>
       <c r="G35" s="3">
-        <v>13680800</v>
+        <v>14409300</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1478,16 +1478,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>5386400</v>
+        <v>5673200</v>
       </c>
       <c r="E41" s="3">
-        <v>6163700</v>
+        <v>6492000</v>
       </c>
       <c r="F41" s="3">
-        <v>7815700</v>
+        <v>8231900</v>
       </c>
       <c r="G41" s="3">
-        <v>5855000</v>
+        <v>6166800</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1505,16 +1505,16 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1157600</v>
+        <v>1219200</v>
       </c>
       <c r="E42" s="3">
-        <v>1315300</v>
+        <v>1385300</v>
       </c>
       <c r="F42" s="3">
-        <v>7836900</v>
+        <v>8254200</v>
       </c>
       <c r="G42" s="3">
-        <v>3773600</v>
+        <v>3974600</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1532,16 +1532,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13733300</v>
+        <v>14464700</v>
       </c>
       <c r="E43" s="3">
-        <v>13869800</v>
+        <v>14608400</v>
       </c>
       <c r="F43" s="3">
-        <v>13822800</v>
+        <v>14558900</v>
       </c>
       <c r="G43" s="3">
-        <v>12810600</v>
+        <v>13492800</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1559,16 +1559,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>13305000</v>
+        <v>14013500</v>
       </c>
       <c r="E44" s="3">
-        <v>16797900</v>
+        <v>17692400</v>
       </c>
       <c r="F44" s="3">
-        <v>13401100</v>
+        <v>14114800</v>
       </c>
       <c r="G44" s="3">
-        <v>11297400</v>
+        <v>11899000</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1586,16 +1586,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>929400</v>
+        <v>978900</v>
       </c>
       <c r="E45" s="3">
-        <v>1068100</v>
+        <v>1125000</v>
       </c>
       <c r="F45" s="3">
-        <v>1030100</v>
+        <v>1084900</v>
       </c>
       <c r="G45" s="3">
-        <v>4366400</v>
+        <v>4598900</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1613,16 +1613,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>34511700</v>
+        <v>36349500</v>
       </c>
       <c r="E46" s="3">
-        <v>39214700</v>
+        <v>41303000</v>
       </c>
       <c r="F46" s="3">
-        <v>43906600</v>
+        <v>46244700</v>
       </c>
       <c r="G46" s="3">
-        <v>38103000</v>
+        <v>40132100</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1640,16 +1640,16 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>17934200</v>
+        <v>18889200</v>
       </c>
       <c r="E47" s="3">
-        <v>18203700</v>
+        <v>19173100</v>
       </c>
       <c r="F47" s="3">
-        <v>16362800</v>
+        <v>17234100</v>
       </c>
       <c r="G47" s="3">
-        <v>16328100</v>
+        <v>17197600</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
@@ -1667,16 +1667,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34075500</v>
+        <v>35890100</v>
       </c>
       <c r="E48" s="3">
-        <v>33710900</v>
+        <v>35506100</v>
       </c>
       <c r="F48" s="3">
-        <v>31702200</v>
+        <v>33390400</v>
       </c>
       <c r="G48" s="3">
-        <v>28900500</v>
+        <v>30439500</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1694,16 +1694,16 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>52475000</v>
+        <v>55269400</v>
       </c>
       <c r="E49" s="3">
-        <v>57598500</v>
+        <v>60665800</v>
       </c>
       <c r="F49" s="3">
-        <v>59540200</v>
+        <v>62710800</v>
       </c>
       <c r="G49" s="3">
-        <v>53425600</v>
+        <v>56270700</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1775,16 +1775,16 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2542200</v>
+        <v>2677600</v>
       </c>
       <c r="E52" s="3">
-        <v>2465000</v>
+        <v>2596300</v>
       </c>
       <c r="F52" s="3">
-        <v>4110300</v>
+        <v>4329100</v>
       </c>
       <c r="G52" s="3">
-        <v>1960600</v>
+        <v>2065000</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -1829,16 +1829,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>141539000</v>
+        <v>149076000</v>
       </c>
       <c r="E54" s="3">
-        <v>151193000</v>
+        <v>159244000</v>
       </c>
       <c r="F54" s="3">
-        <v>155622000</v>
+        <v>163909000</v>
       </c>
       <c r="G54" s="3">
-        <v>138718000</v>
+        <v>146105000</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -1882,16 +1882,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15876300</v>
+        <v>16721700</v>
       </c>
       <c r="E57" s="3">
-        <v>17669100</v>
+        <v>18610000</v>
       </c>
       <c r="F57" s="3">
-        <v>17475600</v>
+        <v>18406300</v>
       </c>
       <c r="G57" s="3">
-        <v>15436700</v>
+        <v>16258800</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -1909,16 +1909,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10531200</v>
+        <v>11092000</v>
       </c>
       <c r="E58" s="3">
-        <v>12182000</v>
+        <v>12830800</v>
       </c>
       <c r="F58" s="3">
-        <v>11287300</v>
+        <v>11888400</v>
       </c>
       <c r="G58" s="3">
-        <v>13442500</v>
+        <v>14158400</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -1936,16 +1936,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>15068700</v>
+        <v>15871200</v>
       </c>
       <c r="E59" s="3">
-        <v>14859600</v>
+        <v>15650900</v>
       </c>
       <c r="F59" s="3">
-        <v>15997000</v>
+        <v>16848900</v>
       </c>
       <c r="G59" s="3">
-        <v>15547400</v>
+        <v>16375400</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -1963,16 +1963,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>41476200</v>
+        <v>43685000</v>
       </c>
       <c r="E60" s="3">
-        <v>44710800</v>
+        <v>47091700</v>
       </c>
       <c r="F60" s="3">
-        <v>44760000</v>
+        <v>47143600</v>
       </c>
       <c r="G60" s="3">
-        <v>44426700</v>
+        <v>46792500</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -1990,16 +1990,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>51252500</v>
+        <v>53981800</v>
       </c>
       <c r="E61" s="3">
-        <v>48562700</v>
+        <v>51148800</v>
       </c>
       <c r="F61" s="3">
-        <v>40802900</v>
+        <v>42975800</v>
       </c>
       <c r="G61" s="3">
-        <v>31235800</v>
+        <v>32899200</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2017,16 +2017,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>8113200</v>
+        <v>8545200</v>
       </c>
       <c r="E62" s="3">
-        <v>10059200</v>
+        <v>10594900</v>
       </c>
       <c r="F62" s="3">
-        <v>9968700</v>
+        <v>10499500</v>
       </c>
       <c r="G62" s="3">
-        <v>11032300</v>
+        <v>11619800</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2125,16 +2125,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>101563000</v>
+        <v>106972000</v>
       </c>
       <c r="E66" s="3">
-        <v>104239000</v>
+        <v>109790000</v>
       </c>
       <c r="F66" s="3">
-        <v>96188100</v>
+        <v>101310000</v>
       </c>
       <c r="G66" s="3">
-        <v>87610800</v>
+        <v>92276300</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2273,16 +2273,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>76067300</v>
+        <v>80118100</v>
       </c>
       <c r="E72" s="3">
-        <v>83413300</v>
+        <v>87855200</v>
       </c>
       <c r="F72" s="3">
-        <v>90754700</v>
+        <v>95587600</v>
       </c>
       <c r="G72" s="3">
-        <v>85482400</v>
+        <v>90034500</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2381,16 +2381,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>39975300</v>
+        <v>42104100</v>
       </c>
       <c r="E76" s="3">
-        <v>46954300</v>
+        <v>49454800</v>
       </c>
       <c r="F76" s="3">
-        <v>59433900</v>
+        <v>62598900</v>
       </c>
       <c r="G76" s="3">
-        <v>51107100</v>
+        <v>53828700</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2467,16 +2467,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>12536600</v>
+        <v>13204200</v>
       </c>
       <c r="E81" s="3">
-        <v>10367900</v>
+        <v>10920100</v>
       </c>
       <c r="F81" s="3">
-        <v>18907200</v>
+        <v>19914100</v>
       </c>
       <c r="G81" s="3">
-        <v>13680800</v>
+        <v>14409300</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2507,16 +2507,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>3867600</v>
+        <v>4073500</v>
       </c>
       <c r="E83" s="3">
-        <v>3960400</v>
+        <v>4171300</v>
       </c>
       <c r="F83" s="3">
-        <v>3847400</v>
+        <v>4052300</v>
       </c>
       <c r="G83" s="3">
-        <v>3875400</v>
+        <v>4081800</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2669,16 +2669,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>17829100</v>
+        <v>18778500</v>
       </c>
       <c r="E89" s="3">
-        <v>13317300</v>
+        <v>14026400</v>
       </c>
       <c r="F89" s="3">
-        <v>15506100</v>
+        <v>16331800</v>
       </c>
       <c r="G89" s="3">
-        <v>16079800</v>
+        <v>16936100</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2709,16 +2709,16 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6390800</v>
+        <v>-6731100</v>
       </c>
       <c r="E91" s="3">
-        <v>-5698500</v>
+        <v>-6001900</v>
       </c>
       <c r="F91" s="3">
-        <v>-5458000</v>
+        <v>-5748600</v>
       </c>
       <c r="G91" s="3">
-        <v>-4558800</v>
+        <v>-4801500</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -2790,16 +2790,16 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-6929900</v>
+        <v>-7298900</v>
       </c>
       <c r="E94" s="3">
-        <v>-2128400</v>
+        <v>-2241700</v>
       </c>
       <c r="F94" s="3">
-        <v>-3404500</v>
+        <v>-3585800</v>
       </c>
       <c r="G94" s="3">
-        <v>-6338200</v>
+        <v>-6675700</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -2830,16 +2830,16 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8756300</v>
+        <v>-9222600</v>
       </c>
       <c r="E96" s="3">
-        <v>-8520300</v>
+        <v>-8974000</v>
       </c>
       <c r="F96" s="3">
-        <v>-8590700</v>
+        <v>-9048200</v>
       </c>
       <c r="G96" s="3">
-        <v>-8612000</v>
+        <v>-9070600</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -2938,16 +2938,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-10913700</v>
+        <v>-11494900</v>
       </c>
       <c r="E100" s="3">
-        <v>-12733400</v>
+        <v>-13411500</v>
       </c>
       <c r="F100" s="3">
-        <v>-10236000</v>
+        <v>-10781100</v>
       </c>
       <c r="G100" s="3">
-        <v>-11611600</v>
+        <v>-12230000</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -2965,16 +2965,16 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-762800</v>
+        <v>-803400</v>
       </c>
       <c r="E101" s="3">
-        <v>-111800</v>
+        <v>-117800</v>
       </c>
       <c r="F101" s="3">
-        <v>99500</v>
+        <v>104800</v>
       </c>
       <c r="G101" s="3">
-        <v>-628600</v>
+        <v>-662000</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -2992,16 +2992,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-777300</v>
+        <v>-818700</v>
       </c>
       <c r="E102" s="3">
-        <v>-1656400</v>
+        <v>-1744600</v>
       </c>
       <c r="F102" s="3">
-        <v>1965100</v>
+        <v>2069700</v>
       </c>
       <c r="G102" s="3">
-        <v>-2498600</v>
+        <v>-2631700</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/NSRGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NSRGY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
   <si>
     <t>NSRGY</t>
   </si>
@@ -31,9 +31,6 @@
   </si>
   <si>
     <t>Period Ending</t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
   <si>
     <t>Total Revenue</t>
@@ -662,8 +659,7 @@
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -693,101 +689,101 @@
       <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="H7" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I7" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J7" s="2">
+        <v>43100</v>
       </c>
       <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>109551600</v>
+        <v>110860300</v>
       </c>
       <c r="E8" s="3">
-        <v>111231500</v>
+        <v>102501400</v>
       </c>
       <c r="F8" s="3">
-        <v>102589700</v>
+        <v>95951100</v>
       </c>
       <c r="G8" s="3">
-        <v>99356100</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>95711800</v>
+      </c>
+      <c r="H8" s="3">
+        <v>95886400</v>
+      </c>
+      <c r="I8" s="3">
+        <v>93245700</v>
+      </c>
+      <c r="J8" s="3">
+        <v>92269300</v>
       </c>
       <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>59286400</v>
+        <v>59767700</v>
       </c>
       <c r="E9" s="3">
-        <v>60955600</v>
+        <v>55960500</v>
       </c>
       <c r="F9" s="3">
-        <v>53561300</v>
+        <v>49876600</v>
       </c>
       <c r="G9" s="3">
-        <v>50619800</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>48568500</v>
+      </c>
+      <c r="H9" s="3">
+        <v>48164700</v>
+      </c>
+      <c r="I9" s="3">
+        <v>46821000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>46760600</v>
       </c>
       <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>50265300</v>
+        <v>51092600</v>
       </c>
       <c r="E10" s="3">
-        <v>50275900</v>
+        <v>46540900</v>
       </c>
       <c r="F10" s="3">
-        <v>49028400</v>
+        <v>46074500</v>
       </c>
       <c r="G10" s="3">
-        <v>48736200</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>47143300</v>
+      </c>
+      <c r="H10" s="3">
+        <v>47721700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>46424700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>45508700</v>
       </c>
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -800,34 +796,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>1950800</v>
+        <v>1966600</v>
       </c>
       <c r="E12" s="3">
-        <v>1997900</v>
+        <v>1834200</v>
       </c>
       <c r="F12" s="3">
-        <v>1967300</v>
+        <v>1831900</v>
       </c>
       <c r="G12" s="3">
-        <v>1856500</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+        <v>1781300</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1726400</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1714500</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1784400</v>
       </c>
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="3">
         <v>0</v>
@@ -854,55 +850,55 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>1894200</v>
+        <v>1954700</v>
       </c>
       <c r="E14" s="3">
-        <v>3936900</v>
+        <v>3652100</v>
       </c>
       <c r="F14" s="3">
-        <v>3947500</v>
+        <v>3355600</v>
       </c>
       <c r="G14" s="3">
-        <v>-598400</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
+        <v>-438500</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1767300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>4867800</v>
       </c>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2966500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2801000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>2747900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2872000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2868400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>3062100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>3135800</v>
       </c>
       <c r="K15" s="3"/>
     </row>
@@ -918,61 +914,61 @@
     </row>
     <row r="17" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>92985400</v>
+        <v>92265400</v>
       </c>
       <c r="E17" s="3">
-        <v>96711400</v>
+        <v>85578600</v>
       </c>
       <c r="F17" s="3">
-        <v>88831800</v>
+        <v>79891600</v>
       </c>
       <c r="G17" s="3">
-        <v>81926400</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>79566000</v>
+      </c>
+      <c r="H17" s="3">
+        <v>79471100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>77655600</v>
+      </c>
+      <c r="J17" s="3">
+        <v>77186600</v>
       </c>
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>16566200</v>
+        <v>18594900</v>
       </c>
       <c r="E18" s="3">
-        <v>14520000</v>
+        <v>16922800</v>
       </c>
       <c r="F18" s="3">
-        <v>13757900</v>
+        <v>16059500</v>
       </c>
       <c r="G18" s="3">
-        <v>17429700</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>16145800</v>
+      </c>
+      <c r="H18" s="3">
+        <v>16415200</v>
+      </c>
+      <c r="I18" s="3">
+        <v>15590100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>15082700</v>
       </c>
       <c r="K18" s="3"/>
     </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -985,142 +981,142 @@
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>164900</v>
+        <v>-1328900</v>
       </c>
       <c r="E20" s="3">
-        <v>99000</v>
+        <v>-1123600</v>
       </c>
       <c r="F20" s="3">
-        <v>-68300</v>
+        <v>-9487600</v>
       </c>
       <c r="G20" s="3">
-        <v>-50700</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+        <v>-2054800</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-1031500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-928900</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-840400</v>
       </c>
       <c r="K20" s="3"/>
     </row>
     <row r="21" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>20794600</v>
+        <v>22890300</v>
       </c>
       <c r="E21" s="3">
-        <v>18780000</v>
+        <v>20847400</v>
       </c>
       <c r="F21" s="3">
-        <v>17731800</v>
+        <v>28295000</v>
       </c>
       <c r="G21" s="3">
-        <v>21450700</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>21072600</v>
+      </c>
+      <c r="H21" s="3">
+        <v>20315100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>19581100</v>
+      </c>
+      <c r="J21" s="3">
+        <v>19058900</v>
       </c>
       <c r="K21" s="3"/>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>1767000</v>
+        <v>1781300</v>
       </c>
       <c r="E22" s="3">
-        <v>1324100</v>
+        <v>1215600</v>
       </c>
       <c r="F22" s="3">
-        <v>960100</v>
+        <v>894000</v>
       </c>
       <c r="G22" s="3">
-        <v>978900</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+        <v>939200</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1059400</v>
+      </c>
+      <c r="I22" s="3">
+        <v>833400</v>
+      </c>
+      <c r="J22" s="3">
+        <v>628000</v>
       </c>
       <c r="K22" s="3"/>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>14964100</v>
+        <v>16415700</v>
       </c>
       <c r="E23" s="3">
-        <v>13294900</v>
+        <v>13330200</v>
       </c>
       <c r="F23" s="3">
-        <v>12729500</v>
+        <v>21343600</v>
       </c>
       <c r="G23" s="3">
-        <v>16400100</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+        <v>17786900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>16585600</v>
+      </c>
+      <c r="I23" s="3">
+        <v>14133700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>10552500</v>
       </c>
       <c r="K23" s="3"/>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>2725900</v>
+        <v>2748000</v>
       </c>
       <c r="E24" s="3">
-        <v>3215900</v>
+        <v>2952400</v>
       </c>
       <c r="F24" s="3">
-        <v>2663500</v>
+        <v>2480200</v>
       </c>
       <c r="G24" s="3">
-        <v>3964000</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+        <v>3803300</v>
+      </c>
+      <c r="H24" s="3">
+        <v>3261800</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3495100</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2845400</v>
       </c>
       <c r="K24" s="3"/>
     </row>
     <row r="25" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="3">
         <v>0</v>
@@ -1147,61 +1143,61 @@
     </row>
     <row r="26" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>12238200</v>
+        <v>13667700</v>
       </c>
       <c r="E26" s="3">
-        <v>10079000</v>
+        <v>10377800</v>
       </c>
       <c r="F26" s="3">
-        <v>10066000</v>
+        <v>18863300</v>
       </c>
       <c r="G26" s="3">
-        <v>12436100</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+        <v>13983600</v>
+      </c>
+      <c r="H26" s="3">
+        <v>13323800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>10638600</v>
+      </c>
+      <c r="J26" s="3">
+        <v>7707100</v>
       </c>
       <c r="K26" s="3"/>
     </row>
     <row r="27" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>13204200</v>
+        <v>13311400</v>
       </c>
       <c r="E27" s="3">
-        <v>10920100</v>
+        <v>10025200</v>
       </c>
       <c r="F27" s="3">
-        <v>19914100</v>
+        <v>18544100</v>
       </c>
       <c r="G27" s="3">
-        <v>14409300</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+        <v>13825400</v>
+      </c>
+      <c r="H27" s="3">
+        <v>13019200</v>
+      </c>
+      <c r="I27" s="3">
+        <v>10300200</v>
+      </c>
+      <c r="J27" s="3">
+        <v>7342800</v>
       </c>
       <c r="K27" s="3"/>
     </row>
     <row r="28" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28" s="3">
         <v>0</v>
@@ -1228,7 +1224,7 @@
     </row>
     <row r="29" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D29" s="3">
         <v>0</v>
@@ -1255,7 +1251,7 @@
     </row>
     <row r="30" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D30" s="3">
         <v>0</v>
@@ -1282,7 +1278,7 @@
     </row>
     <row r="31" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" s="3">
         <v>0</v>
@@ -1309,61 +1305,61 @@
     </row>
     <row r="32" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-164900</v>
+        <v>1328900</v>
       </c>
       <c r="E32" s="3">
-        <v>-99000</v>
+        <v>1123600</v>
       </c>
       <c r="F32" s="3">
-        <v>68300</v>
+        <v>9487600</v>
       </c>
       <c r="G32" s="3">
-        <v>50700</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+        <v>2054800</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1031500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>928900</v>
+      </c>
+      <c r="J32" s="3">
+        <v>840400</v>
       </c>
       <c r="K32" s="3"/>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>13204200</v>
+        <v>13311400</v>
       </c>
       <c r="E33" s="3">
-        <v>10920100</v>
+        <v>10025200</v>
       </c>
       <c r="F33" s="3">
-        <v>19914100</v>
+        <v>18544100</v>
       </c>
       <c r="G33" s="3">
-        <v>14409300</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+        <v>13825400</v>
+      </c>
+      <c r="H33" s="3">
+        <v>13019200</v>
+      </c>
+      <c r="I33" s="3">
+        <v>10300200</v>
+      </c>
+      <c r="J33" s="3">
+        <v>7342800</v>
       </c>
       <c r="K33" s="3"/>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" s="3">
         <v>0</v>
@@ -1390,34 +1386,34 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>13204200</v>
+        <v>13311400</v>
       </c>
       <c r="E35" s="3">
-        <v>10920100</v>
+        <v>10025200</v>
       </c>
       <c r="F35" s="3">
-        <v>19914100</v>
+        <v>18544100</v>
       </c>
       <c r="G35" s="3">
-        <v>14409300</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+        <v>13825400</v>
+      </c>
+      <c r="H35" s="3">
+        <v>13019200</v>
+      </c>
+      <c r="I35" s="3">
+        <v>10300200</v>
+      </c>
+      <c r="J35" s="3">
+        <v>7342800</v>
       </c>
       <c r="K35" s="3"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.2">
@@ -1436,20 +1432,20 @@
       <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="H38" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I38" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J38" s="2">
+        <v>43100</v>
       </c>
       <c r="K38" s="2"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -1462,7 +1458,7 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -1475,250 +1471,250 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>5673200</v>
+        <v>5719300</v>
       </c>
       <c r="E41" s="3">
-        <v>6492000</v>
+        <v>5960000</v>
       </c>
       <c r="F41" s="3">
-        <v>8231900</v>
+        <v>7665600</v>
       </c>
       <c r="G41" s="3">
-        <v>6166800</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+        <v>5916900</v>
+      </c>
+      <c r="H41" s="3">
+        <v>7712000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>4573400</v>
+      </c>
+      <c r="J41" s="3">
+        <v>8145200</v>
       </c>
       <c r="K41" s="3"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>1219200</v>
+        <v>1229100</v>
       </c>
       <c r="E42" s="3">
-        <v>1385300</v>
+        <v>1333400</v>
       </c>
       <c r="F42" s="3">
-        <v>8254200</v>
+        <v>7733600</v>
       </c>
       <c r="G42" s="3">
-        <v>3974600</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+        <v>3922000</v>
+      </c>
+      <c r="H42" s="3">
+        <v>2943800</v>
+      </c>
+      <c r="I42" s="3">
+        <v>5952500</v>
+      </c>
+      <c r="J42" s="3">
+        <v>828100</v>
       </c>
       <c r="K42" s="3"/>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>14464700</v>
+        <v>14582100</v>
       </c>
       <c r="E43" s="3">
-        <v>14608400</v>
+        <v>13411300</v>
       </c>
       <c r="F43" s="3">
-        <v>14558900</v>
+        <v>13557300</v>
       </c>
       <c r="G43" s="3">
-        <v>13492800</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+        <v>12946000</v>
+      </c>
+      <c r="H43" s="3">
+        <v>12941800</v>
+      </c>
+      <c r="I43" s="3">
+        <v>12232200</v>
+      </c>
+      <c r="J43" s="3">
+        <v>13291100</v>
       </c>
       <c r="K43" s="3"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>14013500</v>
+        <v>14127300</v>
       </c>
       <c r="E44" s="3">
-        <v>17692400</v>
+        <v>16242600</v>
       </c>
       <c r="F44" s="3">
-        <v>14114800</v>
+        <v>13143800</v>
       </c>
       <c r="G44" s="3">
-        <v>11899000</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>3</v>
+        <v>11416800</v>
+      </c>
+      <c r="H44" s="3">
+        <v>9647000</v>
+      </c>
+      <c r="I44" s="3">
+        <v>9273800</v>
+      </c>
+      <c r="J44" s="3">
+        <v>9416600</v>
       </c>
       <c r="K44" s="3"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>978900</v>
+        <v>368100</v>
       </c>
       <c r="E45" s="3">
-        <v>1125000</v>
+        <v>377400</v>
       </c>
       <c r="F45" s="3">
-        <v>1084900</v>
+        <v>332400</v>
       </c>
       <c r="G45" s="3">
-        <v>4598900</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
+        <v>3764900</v>
+      </c>
+      <c r="H45" s="3">
+        <v>3064600</v>
+      </c>
+      <c r="I45" s="3">
+        <v>9101000</v>
+      </c>
+      <c r="J45" s="3">
+        <v>447400</v>
       </c>
       <c r="K45" s="3"/>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>36349500</v>
+        <v>36644700</v>
       </c>
       <c r="E46" s="3">
-        <v>41303000</v>
+        <v>37918400</v>
       </c>
       <c r="F46" s="3">
-        <v>46244700</v>
+        <v>43063400</v>
       </c>
       <c r="G46" s="3">
-        <v>40132100</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
+        <v>38505800</v>
+      </c>
+      <c r="H46" s="3">
+        <v>36823300</v>
+      </c>
+      <c r="I46" s="3">
+        <v>41671400</v>
+      </c>
+      <c r="J46" s="3">
+        <v>32716300</v>
       </c>
       <c r="K46" s="3"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>18889200</v>
+        <v>19042600</v>
       </c>
       <c r="E47" s="3">
-        <v>19173100</v>
+        <v>17602000</v>
       </c>
       <c r="F47" s="3">
-        <v>17234100</v>
+        <v>16048500</v>
       </c>
       <c r="G47" s="3">
-        <v>17197600</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+        <v>16500700</v>
+      </c>
+      <c r="H47" s="3">
+        <v>14575300</v>
+      </c>
+      <c r="I47" s="3">
+        <v>13576800</v>
+      </c>
+      <c r="J47" s="3">
+        <v>18091200</v>
       </c>
       <c r="K47" s="3"/>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>35890100</v>
+        <v>36181500</v>
       </c>
       <c r="E48" s="3">
-        <v>35506100</v>
+        <v>32596500</v>
       </c>
       <c r="F48" s="3">
-        <v>33390400</v>
+        <v>31093300</v>
       </c>
       <c r="G48" s="3">
-        <v>30439500</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+        <v>29206000</v>
+      </c>
+      <c r="H48" s="3">
+        <v>29697800</v>
+      </c>
+      <c r="I48" s="3">
+        <v>30444300</v>
+      </c>
+      <c r="J48" s="3">
+        <v>31580400</v>
       </c>
       <c r="K48" s="3"/>
     </row>
     <row r="49" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>55269400</v>
+        <v>55718100</v>
       </c>
       <c r="E49" s="3">
-        <v>60665800</v>
+        <v>55694500</v>
       </c>
       <c r="F49" s="3">
-        <v>62710800</v>
+        <v>58396700</v>
       </c>
       <c r="G49" s="3">
-        <v>56270700</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
+        <v>53990400</v>
+      </c>
+      <c r="H49" s="3">
+        <v>48240000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>51156600</v>
+      </c>
+      <c r="J49" s="3">
+        <v>51675600</v>
       </c>
       <c r="K49" s="3"/>
     </row>
     <row r="50" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D50" s="3">
         <v>0</v>
@@ -1745,7 +1741,7 @@
     </row>
     <row r="51" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D51" s="3">
         <v>0</v>
@@ -1772,34 +1768,34 @@
     </row>
     <row r="52" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>2677600</v>
+        <v>1296800</v>
       </c>
       <c r="E52" s="3">
-        <v>2596300</v>
+        <v>1255600</v>
       </c>
       <c r="F52" s="3">
-        <v>4329100</v>
+        <v>2651400</v>
       </c>
       <c r="G52" s="3">
-        <v>2065000</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+        <v>529000</v>
+      </c>
+      <c r="H52" s="3">
+        <v>583400</v>
+      </c>
+      <c r="I52" s="3">
+        <v>553900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>465900</v>
       </c>
       <c r="K52" s="3"/>
     </row>
     <row r="53" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D53" s="3">
         <v>0</v>
@@ -1826,34 +1822,34 @@
     </row>
     <row r="54" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>149076000</v>
+        <v>150286200</v>
       </c>
       <c r="E54" s="3">
-        <v>159244000</v>
+        <v>146194900</v>
       </c>
       <c r="F54" s="3">
-        <v>163909000</v>
+        <v>152633300</v>
       </c>
       <c r="G54" s="3">
-        <v>146105000</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+        <v>140184200</v>
+      </c>
+      <c r="H54" s="3">
+        <v>132102600</v>
+      </c>
+      <c r="I54" s="3">
+        <v>139248500</v>
+      </c>
+      <c r="J54" s="3">
+        <v>136687300</v>
       </c>
       <c r="K54" s="3"/>
     </row>
     <row r="55" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -1866,7 +1862,7 @@
     </row>
     <row r="56" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -1879,169 +1875,169 @@
     </row>
     <row r="57" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>16721700</v>
+        <v>16857500</v>
       </c>
       <c r="E57" s="3">
-        <v>18610000</v>
+        <v>17085000</v>
       </c>
       <c r="F57" s="3">
-        <v>18406300</v>
+        <v>17140000</v>
       </c>
       <c r="G57" s="3">
-        <v>16258800</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>15599900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>14473000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>13257700</v>
+      </c>
+      <c r="J57" s="3">
+        <v>13226500</v>
       </c>
       <c r="K57" s="3"/>
     </row>
     <row r="58" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>11092000</v>
+        <v>11182100</v>
       </c>
       <c r="E58" s="3">
-        <v>12830800</v>
+        <v>11779300</v>
       </c>
       <c r="F58" s="3">
-        <v>11888400</v>
+        <v>11420500</v>
       </c>
       <c r="G58" s="3">
-        <v>14158400</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>13686400</v>
+      </c>
+      <c r="H58" s="3">
+        <v>14791100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>15228300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>11850500</v>
       </c>
       <c r="K58" s="3"/>
     </row>
     <row r="59" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>15871200</v>
+        <v>7951900</v>
       </c>
       <c r="E59" s="3">
-        <v>15650900</v>
+        <v>6927900</v>
       </c>
       <c r="F59" s="3">
-        <v>16848900</v>
+        <v>7745600</v>
       </c>
       <c r="G59" s="3">
-        <v>16375400</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+        <v>7853100</v>
+      </c>
+      <c r="H59" s="3">
+        <v>7104900</v>
+      </c>
+      <c r="I59" s="3">
+        <v>9138600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>7356100</v>
       </c>
       <c r="K59" s="3"/>
     </row>
     <row r="60" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>43685000</v>
+        <v>44039600</v>
       </c>
       <c r="E60" s="3">
-        <v>47091700</v>
+        <v>43232700</v>
       </c>
       <c r="F60" s="3">
-        <v>47143600</v>
+        <v>43900400</v>
       </c>
       <c r="G60" s="3">
-        <v>46792500</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
+        <v>44896300</v>
+      </c>
+      <c r="H60" s="3">
+        <v>42969000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>43731500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>39185900</v>
       </c>
       <c r="K60" s="3"/>
     </row>
     <row r="61" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>53981800</v>
+        <v>54420100</v>
       </c>
       <c r="E61" s="3">
-        <v>51148800</v>
+        <v>46957300</v>
       </c>
       <c r="F61" s="3">
-        <v>42975800</v>
+        <v>40019300</v>
       </c>
       <c r="G61" s="3">
-        <v>32899200</v>
+        <v>31566000</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>23884600</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>26118900</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>19050600</v>
       </c>
       <c r="K61" s="3"/>
     </row>
     <row r="62" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>8545200</v>
+        <v>1959500</v>
       </c>
       <c r="E62" s="3">
-        <v>10594900</v>
+        <v>2637700</v>
       </c>
       <c r="F62" s="3">
-        <v>10499500</v>
+        <v>1469900</v>
       </c>
       <c r="G62" s="3">
-        <v>11619800</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>2384900</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1642800</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1446200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>3717600</v>
       </c>
       <c r="K62" s="3"/>
     </row>
     <row r="63" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D63" s="3">
         <v>0</v>
@@ -2068,7 +2064,7 @@
     </row>
     <row r="64" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D64" s="3">
         <v>0</v>
@@ -2095,7 +2091,7 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D65" s="3">
         <v>0</v>
@@ -2122,34 +2118,34 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>106972000</v>
+        <v>107074300</v>
       </c>
       <c r="E66" s="3">
-        <v>109790000</v>
+        <v>99916700</v>
       </c>
       <c r="F66" s="3">
-        <v>101310000</v>
+        <v>93696900</v>
       </c>
       <c r="G66" s="3">
-        <v>92276300</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+        <v>87611200</v>
+      </c>
+      <c r="H66" s="3">
+        <v>77520700</v>
+      </c>
+      <c r="I66" s="3">
+        <v>79893500</v>
+      </c>
+      <c r="J66" s="3">
+        <v>72833900</v>
       </c>
       <c r="K66" s="3"/>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -2162,7 +2158,7 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D68" s="3">
         <v>0</v>
@@ -2189,7 +2185,7 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D69" s="3">
         <v>0</v>
@@ -2216,7 +2212,7 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D70" s="3">
         <v>0</v>
@@ -2243,7 +2239,7 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D71" s="3">
         <v>0</v>
@@ -2270,34 +2266,34 @@
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>80118100</v>
+        <v>81064300</v>
       </c>
       <c r="E72" s="3">
-        <v>87855200</v>
+        <v>80712000</v>
       </c>
       <c r="F72" s="3">
-        <v>95587600</v>
+        <v>89252000</v>
       </c>
       <c r="G72" s="3">
-        <v>90034500</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+        <v>86817700</v>
+      </c>
+      <c r="H72" s="3">
+        <v>85762400</v>
+      </c>
+      <c r="I72" s="3">
+        <v>85999400</v>
+      </c>
+      <c r="J72" s="3">
+        <v>85812100</v>
       </c>
       <c r="K72" s="3"/>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D73" s="3">
         <v>0</v>
@@ -2324,7 +2320,7 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D74" s="3">
         <v>0</v>
@@ -2351,7 +2347,7 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D75" s="3">
         <v>0</v>
@@ -2378,34 +2374,34 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>42104100</v>
+        <v>42445900</v>
       </c>
       <c r="E76" s="3">
-        <v>49454800</v>
+        <v>45402100</v>
       </c>
       <c r="F76" s="3">
-        <v>62598900</v>
+        <v>58292500</v>
       </c>
       <c r="G76" s="3">
-        <v>53828700</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+        <v>51647400</v>
+      </c>
+      <c r="H76" s="3">
+        <v>53728000</v>
+      </c>
+      <c r="I76" s="3">
+        <v>58298100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>62547200</v>
       </c>
       <c r="K76" s="3"/>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D77" s="3">
         <v>0</v>
@@ -2432,7 +2428,7 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.2">
@@ -2451,47 +2447,47 @@
       <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="H80" s="2">
+        <v>43830</v>
+      </c>
+      <c r="I80" s="2">
+        <v>43465</v>
+      </c>
+      <c r="J80" s="2">
+        <v>43100</v>
       </c>
       <c r="K80" s="2"/>
     </row>
     <row r="81" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>13204200</v>
+        <v>13311400</v>
       </c>
       <c r="E81" s="3">
-        <v>10920100</v>
+        <v>10025200</v>
       </c>
       <c r="F81" s="3">
-        <v>19914100</v>
+        <v>18544100</v>
       </c>
       <c r="G81" s="3">
-        <v>14409300</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+        <v>13825400</v>
+      </c>
+      <c r="H81" s="3">
+        <v>13019200</v>
+      </c>
+      <c r="I81" s="3">
+        <v>10300200</v>
+      </c>
+      <c r="J81" s="3">
+        <v>7342800</v>
       </c>
       <c r="K81" s="3"/>
     </row>
     <row r="82" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -2504,34 +2500,34 @@
     </row>
     <row r="83" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>4073500</v>
+        <v>3554400</v>
       </c>
       <c r="E83" s="3">
-        <v>4171300</v>
+        <v>3349300</v>
       </c>
       <c r="F83" s="3">
-        <v>4052300</v>
+        <v>3352300</v>
       </c>
       <c r="G83" s="3">
-        <v>4081800</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>3534300</v>
+      </c>
+      <c r="H83" s="3">
+        <v>3601500</v>
+      </c>
+      <c r="I83" s="3">
+        <v>3662800</v>
+      </c>
+      <c r="J83" s="3">
+        <v>3652900</v>
       </c>
       <c r="K83" s="3"/>
     </row>
     <row r="84" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D84" s="3">
         <v>0</v>
@@ -2558,7 +2554,7 @@
     </row>
     <row r="85" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D85" s="3">
         <v>0</v>
@@ -2585,7 +2581,7 @@
     </row>
     <row r="86" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D86" s="3">
         <v>0</v>
@@ -2612,7 +2608,7 @@
     </row>
     <row r="87" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D87" s="3">
         <v>0</v>
@@ -2639,7 +2635,7 @@
     </row>
     <row r="88" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D88" s="3">
         <v>0</v>
@@ -2666,34 +2662,34 @@
     </row>
     <row r="89" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>18778500</v>
+        <v>18931000</v>
       </c>
       <c r="E89" s="3">
-        <v>14026400</v>
+        <v>12877000</v>
       </c>
       <c r="F89" s="3">
-        <v>16331800</v>
+        <v>15208300</v>
       </c>
       <c r="G89" s="3">
-        <v>16936100</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>16249800</v>
+      </c>
+      <c r="H89" s="3">
+        <v>16365700</v>
+      </c>
+      <c r="I89" s="3">
+        <v>15649000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>14569700</v>
       </c>
       <c r="K89" s="3"/>
     </row>
     <row r="90" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -2706,34 +2702,34 @@
     </row>
     <row r="91" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-6731100</v>
+        <v>-6785700</v>
       </c>
       <c r="E91" s="3">
-        <v>-6001900</v>
+        <v>-5510100</v>
       </c>
       <c r="F91" s="3">
-        <v>-5748600</v>
+        <v>-5353200</v>
       </c>
       <c r="G91" s="3">
-        <v>-4801500</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+        <v>-4607000</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-3815200</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-3932100</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-4040800</v>
       </c>
       <c r="K91" s="3"/>
     </row>
     <row r="92" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D92" s="3">
         <v>0</v>
@@ -2760,7 +2756,7 @@
     </row>
     <row r="93" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D93" s="3">
         <v>0</v>
@@ -2787,34 +2783,34 @@
     </row>
     <row r="94" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-7298900</v>
+        <v>-7358100</v>
       </c>
       <c r="E94" s="3">
-        <v>-2241700</v>
+        <v>-2058000</v>
       </c>
       <c r="F94" s="3">
-        <v>-3585800</v>
+        <v>-3339100</v>
       </c>
       <c r="G94" s="3">
-        <v>-6675700</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>-6405200</v>
+      </c>
+      <c r="H94" s="3">
+        <v>8627900</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-14498600</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-5079200</v>
       </c>
       <c r="K94" s="3"/>
     </row>
     <row r="95" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -2827,34 +2823,34 @@
     </row>
     <row r="96" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-9222600</v>
+        <v>9297400</v>
       </c>
       <c r="E96" s="3">
-        <v>-8974000</v>
+        <v>8238600</v>
       </c>
       <c r="F96" s="3">
-        <v>-9048200</v>
+        <v>8425800</v>
       </c>
       <c r="G96" s="3">
-        <v>-9070600</v>
+        <v>8703000</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>7465200</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>7240100</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>7312000</v>
       </c>
       <c r="K96" s="3"/>
     </row>
     <row r="97" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D97" s="3">
         <v>0</v>
@@ -2881,7 +2877,7 @@
     </row>
     <row r="98" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D98" s="3">
         <v>0</v>
@@ -2908,7 +2904,7 @@
     </row>
     <row r="99" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D99" s="3">
         <v>0</v>
@@ -2935,82 +2931,82 @@
     </row>
     <row r="100" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-11494900</v>
+        <v>-11588200</v>
       </c>
       <c r="E100" s="3">
-        <v>-13411500</v>
+        <v>-12312500</v>
       </c>
       <c r="F100" s="3">
-        <v>-10781100</v>
+        <v>-10039400</v>
       </c>
       <c r="G100" s="3">
-        <v>-12230000</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>-11734400</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-21844300</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-4184100</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-9321100</v>
       </c>
       <c r="K100" s="3"/>
     </row>
     <row r="101" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-803400</v>
+        <v>-809900</v>
       </c>
       <c r="E101" s="3">
-        <v>-117800</v>
+        <v>-108100</v>
       </c>
       <c r="F101" s="3">
-        <v>104800</v>
+        <v>97600</v>
       </c>
       <c r="G101" s="3">
-        <v>-662000</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>-635200</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-228200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-318100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-222700</v>
       </c>
       <c r="K101" s="3"/>
     </row>
     <row r="102" spans="3:11" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-818700</v>
+        <v>-825400</v>
       </c>
       <c r="E102" s="3">
-        <v>-1744600</v>
+        <v>-1601700</v>
       </c>
       <c r="F102" s="3">
-        <v>2069700</v>
+        <v>1927400</v>
       </c>
       <c r="G102" s="3">
-        <v>-2631700</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>-2525000</v>
+      </c>
+      <c r="H102" s="3">
+        <v>2921000</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-3351800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-53400</v>
       </c>
       <c r="K102" s="3"/>
     </row>

--- a/AAII_Financials/Yearly/NSRGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NSRGY_YR_FIN.xlsx
@@ -653,135 +653,147 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:K102"/>
+  <dimension ref="A5:L102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>101216100</v>
+      </c>
+      <c r="E8" s="3">
         <v>110860300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>102501400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>95951100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>95711800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>95886400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>93245700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>92269300</v>
       </c>
-      <c r="K8" s="3"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L8" s="3"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>53709000</v>
+      </c>
+      <c r="E9" s="3">
         <v>59767700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>55960500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>49876600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>48568500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>48164700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>46821000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>46760600</v>
       </c>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L9" s="3"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>47507100</v>
+      </c>
+      <c r="E10" s="3">
         <v>51092600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>46540900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>46074500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>47143300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>47721700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>46424700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>45508700</v>
       </c>
-      <c r="K10" s="3"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L10" s="3"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -793,35 +805,39 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L11" s="3"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1839600</v>
+      </c>
+      <c r="E12" s="3">
         <v>1966600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1834200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1831900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1781300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1726400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1714500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1784400</v>
       </c>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L12" s="3"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -846,63 +862,72 @@
       <c r="J13" s="3">
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>994300</v>
+      </c>
+      <c r="E14" s="3">
         <v>1954700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3652100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3355600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-438500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-32000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1767300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4867800</v>
       </c>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L14" s="3"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>2873600</v>
+      </c>
+      <c r="E15" s="3">
         <v>2966500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2801000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2747900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2872000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2868400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3062100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3135800</v>
       </c>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L15" s="3"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -911,62 +936,69 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>84030800</v>
+      </c>
+      <c r="E17" s="3">
         <v>92265400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>85578600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>79891600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>79566000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>79471100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>77655600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>77186600</v>
       </c>
-      <c r="K17" s="3"/>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L17" s="3"/>
+    </row>
+    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>17185300</v>
+      </c>
+      <c r="E18" s="3">
         <v>18594900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16922800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>16059500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>16145800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16415200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>15590100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15082700</v>
       </c>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -978,143 +1010,159 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1376100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1328900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1123600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9487600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2054800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1031500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-928900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-840400</v>
       </c>
-      <c r="K20" s="3"/>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L20" s="3"/>
+    </row>
+    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>21435000</v>
+      </c>
+      <c r="E21" s="3">
         <v>22890300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>20847400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28295000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>21072600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>20315100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19581100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19058900</v>
       </c>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>1876000</v>
+      </c>
+      <c r="E22" s="3">
         <v>1781300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1215600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>894000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>939200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1059400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>833400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>628000</v>
       </c>
-      <c r="K22" s="3"/>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L22" s="3"/>
+    </row>
+    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>15988000</v>
+      </c>
+      <c r="E23" s="3">
         <v>16415700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13330200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21343600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17786900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>16585600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14133700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10552500</v>
       </c>
-      <c r="K23" s="3"/>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L23" s="3"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>3657100</v>
+      </c>
+      <c r="E24" s="3">
         <v>2748000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2952400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2480200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3803300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3261800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3495100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2845400</v>
       </c>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L24" s="3"/>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1139,63 +1187,72 @@
       <c r="J25" s="3">
         <v>0</v>
       </c>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3"/>
+    </row>
+    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>12330900</v>
+      </c>
+      <c r="E26" s="3">
         <v>13667700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10377800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18863300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13983600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13323800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10638600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7707100</v>
       </c>
-      <c r="K26" s="3"/>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L26" s="3"/>
+    </row>
+    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>12010900</v>
+      </c>
+      <c r="E27" s="3">
         <v>13311400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10025200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18544100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13825400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13019200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10300200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7342800</v>
       </c>
-      <c r="K27" s="3"/>
-    </row>
-    <row r="28" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L27" s="3"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1220,9 +1277,12 @@
       <c r="J28" s="3">
         <v>0</v>
       </c>
-      <c r="K28" s="3"/>
-    </row>
-    <row r="29" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K28" s="3">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1247,9 +1307,12 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3"/>
-    </row>
-    <row r="30" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1274,9 +1337,12 @@
       <c r="J30" s="3">
         <v>0</v>
       </c>
-      <c r="K30" s="3"/>
-    </row>
-    <row r="31" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1301,63 +1367,72 @@
       <c r="J31" s="3">
         <v>0</v>
       </c>
-      <c r="K31" s="3"/>
-    </row>
-    <row r="32" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>1376100</v>
+      </c>
+      <c r="E32" s="3">
         <v>1328900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1123600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9487600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2054800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1031500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>928900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>840400</v>
       </c>
-      <c r="K32" s="3"/>
-    </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L32" s="3"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>12010900</v>
+      </c>
+      <c r="E33" s="3">
         <v>13311400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10025200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18544100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13825400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13019200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10300200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7342800</v>
       </c>
-      <c r="K33" s="3"/>
-    </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1382,68 +1457,77 @@
       <c r="J34" s="3">
         <v>0</v>
       </c>
-      <c r="K34" s="3"/>
-    </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K34" s="3">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>12010900</v>
+      </c>
+      <c r="E35" s="3">
         <v>13311400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10025200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18544100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13825400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13019200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10300200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7342800</v>
       </c>
-      <c r="K35" s="3"/>
-    </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L35" s="3"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1455,8 +1539,9 @@
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
-    </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1468,251 +1553,279 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L40" s="3"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>6131200</v>
+      </c>
+      <c r="E41" s="3">
         <v>5719300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5960000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7665600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5916900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7712000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4573400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8145200</v>
       </c>
-      <c r="K41" s="3"/>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>2554700</v>
+      </c>
+      <c r="E42" s="3">
         <v>1229100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1333400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7733600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3922000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2943800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5952500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>828100</v>
       </c>
-      <c r="K42" s="3"/>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>13888000</v>
+      </c>
+      <c r="E43" s="3">
         <v>14582100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>13411300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13557300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12946000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12941800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12232200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>13291100</v>
       </c>
-      <c r="K43" s="3"/>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L43" s="3"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>14632900</v>
+      </c>
+      <c r="E44" s="3">
         <v>14127300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16242600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>13143800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11416800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9647000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9273800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9416600</v>
       </c>
-      <c r="K44" s="3"/>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L44" s="3"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>1025200</v>
+      </c>
+      <c r="E45" s="3">
         <v>368100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>377400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>332400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3764900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3064600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9101000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>447400</v>
       </c>
-      <c r="K45" s="3"/>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L45" s="3"/>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>38831100</v>
+      </c>
+      <c r="E46" s="3">
         <v>36644700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>37918400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>43063400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>38505800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>36823300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>41671400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>32716300</v>
       </c>
-      <c r="K46" s="3"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L46" s="3"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>19837100</v>
+      </c>
+      <c r="E47" s="3">
         <v>19042600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>17602000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>16048500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16500700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14575300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>13576800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>18091200</v>
       </c>
-      <c r="K47" s="3"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L47" s="3"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>37195700</v>
+      </c>
+      <c r="E48" s="3">
         <v>36181500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32596500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31093300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29206000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29697800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>30444300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31580400</v>
       </c>
-      <c r="K48" s="3"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L48" s="3"/>
+    </row>
+    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>55000100</v>
+      </c>
+      <c r="E49" s="3">
         <v>55718100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>55694500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>58396700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>53990400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>48240000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>51156600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>51675600</v>
       </c>
-      <c r="K49" s="3"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L49" s="3"/>
+    </row>
+    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1737,9 +1850,12 @@
       <c r="J50" s="3">
         <v>0</v>
       </c>
-      <c r="K50" s="3"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K50" s="3">
+        <v>0</v>
+      </c>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1764,36 +1880,42 @@
       <c r="J51" s="3">
         <v>0</v>
       </c>
-      <c r="K51" s="3"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K51" s="3">
+        <v>0</v>
+      </c>
+      <c r="L51" s="3"/>
+    </row>
+    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>1720400</v>
+      </c>
+      <c r="E52" s="3">
         <v>1296800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1255600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2651400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>529000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>583400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>553900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>465900</v>
       </c>
-      <c r="K52" s="3"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1818,36 +1940,42 @@
       <c r="J53" s="3">
         <v>0</v>
       </c>
-      <c r="K53" s="3"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K53" s="3">
+        <v>0</v>
+      </c>
+      <c r="L53" s="3"/>
+    </row>
+    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>153682500</v>
+      </c>
+      <c r="E54" s="3">
         <v>150286200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>146194900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>152633300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>140184200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>132102600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>139248500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>136687300</v>
       </c>
-      <c r="K54" s="3"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L54" s="3"/>
+    </row>
+    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1859,8 +1987,9 @@
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L55" s="3"/>
+    </row>
+    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -1872,170 +2001,189 @@
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L56" s="3"/>
+    </row>
+    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>18412500</v>
+      </c>
+      <c r="E57" s="3">
         <v>16857500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17085000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17140000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15599900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14473000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13257700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13226500</v>
       </c>
-      <c r="K57" s="3"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L57" s="3"/>
+    </row>
+    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>13091200</v>
+      </c>
+      <c r="E58" s="3">
         <v>11182100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11779300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11420500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13686400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>14791100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>15228300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11850500</v>
       </c>
-      <c r="K58" s="3"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L58" s="3"/>
+    </row>
+    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>7898000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7951900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6927900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7745600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7853100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7104900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9138600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7356100</v>
       </c>
-      <c r="K59" s="3"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L59" s="3"/>
+    </row>
+    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>47300800</v>
+      </c>
+      <c r="E60" s="3">
         <v>44039600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>43232700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>43900400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>44896300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>42969000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>43731500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>39185900</v>
       </c>
-      <c r="K60" s="3"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L60" s="3"/>
+    </row>
+    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>57049400</v>
+      </c>
+      <c r="E61" s="3">
         <v>54420100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>46957300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>40019300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>31566000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>23884600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>26118900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>19050600</v>
       </c>
-      <c r="K61" s="3"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L61" s="3"/>
+    </row>
+    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1782200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1959500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2637700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1469900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2384900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1642800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1446200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3717600</v>
       </c>
-      <c r="K62" s="3"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L62" s="3"/>
+    </row>
+    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2060,9 +2208,12 @@
       <c r="J63" s="3">
         <v>0</v>
       </c>
-      <c r="K63" s="3"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K63" s="3">
+        <v>0</v>
+      </c>
+      <c r="L63" s="3"/>
+    </row>
+    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2087,9 +2238,12 @@
       <c r="J64" s="3">
         <v>0</v>
       </c>
-      <c r="K64" s="3"/>
-    </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" s="3">
+        <v>0</v>
+      </c>
+      <c r="L64" s="3"/>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2114,36 +2268,42 @@
       <c r="J65" s="3">
         <v>0</v>
       </c>
-      <c r="K65" s="3"/>
-    </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3"/>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>113190500</v>
+      </c>
+      <c r="E66" s="3">
         <v>107074300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>99916700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>93696900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>87611200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>77520700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>79893500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>72833900</v>
       </c>
-      <c r="K66" s="3"/>
-    </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L66" s="3"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2155,8 +2315,9 @@
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L67" s="3"/>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2181,9 +2342,12 @@
       <c r="J68" s="3">
         <v>0</v>
       </c>
-      <c r="K68" s="3"/>
-    </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K68" s="3">
+        <v>0</v>
+      </c>
+      <c r="L68" s="3"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2208,9 +2372,12 @@
       <c r="J69" s="3">
         <v>0</v>
       </c>
-      <c r="K69" s="3"/>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,9 +2402,12 @@
       <c r="J70" s="3">
         <v>0</v>
       </c>
-      <c r="K70" s="3"/>
-    </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3"/>
+    </row>
+    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2262,36 +2432,42 @@
       <c r="J71" s="3">
         <v>0</v>
       </c>
-      <c r="K71" s="3"/>
-    </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3"/>
+    </row>
+    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>73233800</v>
+      </c>
+      <c r="E72" s="3">
         <v>81064300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>80712000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>89252000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>86817700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>85762400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>85999400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>85812100</v>
       </c>
-      <c r="K72" s="3"/>
-    </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L72" s="3"/>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2316,9 +2492,12 @@
       <c r="J73" s="3">
         <v>0</v>
       </c>
-      <c r="K73" s="3"/>
-    </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K73" s="3">
+        <v>0</v>
+      </c>
+      <c r="L73" s="3"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2343,9 +2522,12 @@
       <c r="J74" s="3">
         <v>0</v>
       </c>
-      <c r="K74" s="3"/>
-    </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K74" s="3">
+        <v>0</v>
+      </c>
+      <c r="L74" s="3"/>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2370,36 +2552,42 @@
       <c r="J75" s="3">
         <v>0</v>
       </c>
-      <c r="K75" s="3"/>
-    </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K75" s="3">
+        <v>0</v>
+      </c>
+      <c r="L75" s="3"/>
+    </row>
+    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>39635600</v>
+      </c>
+      <c r="E76" s="3">
         <v>42445900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>45402100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>58292500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>51647400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>53728000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>58298100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>62547200</v>
       </c>
-      <c r="K76" s="3"/>
-    </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="L76" s="3"/>
+    </row>
+    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2424,68 +2612,77 @@
       <c r="J77" s="3">
         <v>0</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K77" s="3">
+        <v>0</v>
+      </c>
+      <c r="L77" s="3"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L80" s="2"/>
+    </row>
+    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>12010900</v>
+      </c>
+      <c r="E81" s="3">
         <v>13311400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10025200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18544100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13825400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13019200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10300200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7342800</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L81" s="3"/>
+    </row>
+    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2497,35 +2694,39 @@
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
-    </row>
-    <row r="83" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L82" s="3"/>
+    </row>
+    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>3432000</v>
+      </c>
+      <c r="E83" s="3">
         <v>3554400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3349300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3352300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3534300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3601500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3662800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3652900</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L83" s="3"/>
+    </row>
+    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2550,9 +2751,12 @@
       <c r="J84" s="3">
         <v>0</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K84" s="3">
+        <v>0</v>
+      </c>
+      <c r="L84" s="3"/>
+    </row>
+    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2577,9 +2781,12 @@
       <c r="J85" s="3">
         <v>0</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K85" s="3">
+        <v>0</v>
+      </c>
+      <c r="L85" s="3"/>
+    </row>
+    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2604,9 +2811,12 @@
       <c r="J86" s="3">
         <v>0</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K86" s="3">
+        <v>0</v>
+      </c>
+      <c r="L86" s="3"/>
+    </row>
+    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2631,9 +2841,12 @@
       <c r="J87" s="3">
         <v>0</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K87" s="3">
+        <v>0</v>
+      </c>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2658,36 +2871,42 @@
       <c r="J88" s="3">
         <v>0</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K88" s="3">
+        <v>0</v>
+      </c>
+      <c r="L88" s="3"/>
+    </row>
+    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>18401400</v>
+      </c>
+      <c r="E89" s="3">
         <v>18931000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12877000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>15208300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>16249800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16365700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>15649000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14569700</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L89" s="3"/>
+    </row>
+    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2699,35 +2918,39 @@
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
-    </row>
-    <row r="91" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L90" s="3"/>
+    </row>
+    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-6221700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6785700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5510100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5353200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4607000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3815200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3932100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4040800</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L91" s="3"/>
+    </row>
+    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2752,9 +2975,12 @@
       <c r="J92" s="3">
         <v>0</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K92" s="3">
+        <v>0</v>
+      </c>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -2779,36 +3005,42 @@
       <c r="J93" s="3">
         <v>0</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K93" s="3">
+        <v>0</v>
+      </c>
+      <c r="L93" s="3"/>
+    </row>
+    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-9516900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7358100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2058000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3339100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6405200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>8627900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-14498600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5079200</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L94" s="3"/>
+    </row>
+    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -2820,35 +3052,39 @@
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
-    </row>
-    <row r="96" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L95" s="3"/>
+    </row>
+    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>8625200</v>
+      </c>
+      <c r="E96" s="3">
         <v>9297400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>8238600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>8425800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>8703000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>7465200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>7240100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>7312000</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L96" s="3"/>
+    </row>
+    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -2873,9 +3109,12 @@
       <c r="J97" s="3">
         <v>0</v>
       </c>
-      <c r="K97" s="3"/>
-    </row>
-    <row r="98" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K97" s="3">
+        <v>0</v>
+      </c>
+      <c r="L97" s="3"/>
+    </row>
+    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -2900,9 +3139,12 @@
       <c r="J98" s="3">
         <v>0</v>
       </c>
-      <c r="K98" s="3"/>
-    </row>
-    <row r="99" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K98" s="3">
+        <v>0</v>
+      </c>
+      <c r="L98" s="3"/>
+    </row>
+    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -2927,88 +3169,100 @@
       <c r="J99" s="3">
         <v>0</v>
       </c>
-      <c r="K99" s="3"/>
-    </row>
-    <row r="100" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="K99" s="3">
+        <v>0</v>
+      </c>
+      <c r="L99" s="3"/>
+    </row>
+    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-8124200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11588200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12312500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10039400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11734400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21844300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4184100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9321100</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L100" s="3"/>
+    </row>
+    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-809900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-108100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>97600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-635200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-228200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-318100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-222700</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" spans="3:11" x14ac:dyDescent="0.2">
+      <c r="L101" s="3"/>
+    </row>
+    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>818800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-825400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1601700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1927400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2525000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2921000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3351800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-53400</v>
       </c>
-      <c r="K102" s="3"/>
+      <c r="L102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/NSRGY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NSRGY_YR_FIN.xlsx
@@ -653,147 +653,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>113355200</v>
+      </c>
+      <c r="E8" s="3">
         <v>101216100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>110860300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>102501400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>95951100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>95711800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>95886400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>93245700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>92269300</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>61408700</v>
+      </c>
+      <c r="E9" s="3">
         <v>53709000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>59767700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>55960500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>49876600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>48568500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>48164700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>46821000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>46760600</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>51946500</v>
+      </c>
+      <c r="E10" s="3">
         <v>47507100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>51092600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>46540900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>46074500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>47143300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>47721700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46424700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>45508700</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -806,38 +818,42 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>2034200</v>
+      </c>
+      <c r="E12" s="3">
         <v>1839600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1966600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1834200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1831900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1781300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1726400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1714500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1784400</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,69 +881,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>994300</v>
+        <v>2104800</v>
       </c>
       <c r="E14" s="3">
+        <v>975500</v>
+      </c>
+      <c r="F14" s="3">
         <v>1954700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3652100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3355600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-438500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-32000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1767300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4867800</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>3463000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2873600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2966500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2801000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2747900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2872000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2868400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3062100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3135800</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -937,68 +962,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>84030800</v>
+        <v>95818100</v>
       </c>
       <c r="E17" s="3">
+        <v>84049500</v>
+      </c>
+      <c r="F17" s="3">
         <v>92265400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>85578600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>79891600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>79566000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>79471100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>77655600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>77186600</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>17185300</v>
+        <v>17537000</v>
       </c>
       <c r="E18" s="3">
+        <v>17166600</v>
+      </c>
+      <c r="F18" s="3">
         <v>18594900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>16922800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>16059500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16145800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16415200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15590100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15082700</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1011,158 +1043,174 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1437700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1376100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1328900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1123600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9487600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2054800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1031500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-928900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-840400</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>21435000</v>
+        <v>22437700</v>
       </c>
       <c r="E21" s="3">
+        <v>21416300</v>
+      </c>
+      <c r="F21" s="3">
         <v>22890300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20847400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>28295000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>21072600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>20315100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19581100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19058900</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>2122500</v>
+      </c>
+      <c r="E22" s="3">
         <v>1876000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1781300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1215600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>894000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>939200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1059400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>833400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>628000</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>14999700</v>
+      </c>
+      <c r="E23" s="3">
         <v>15988000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>16415700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>13330200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21343600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17786900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>16585600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14133700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>10552500</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>3329300</v>
+      </c>
+      <c r="E24" s="3">
         <v>3657100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2748000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2952400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2480200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3803300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3261800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3495100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2845400</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1190,69 +1238,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>11670300</v>
+      </c>
+      <c r="E26" s="3">
         <v>12330900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13667700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10377800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>18863300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13983600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13323800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10638600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7707100</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>11391600</v>
+      </c>
+      <c r="E27" s="3">
         <v>12010900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13311400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10025200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>18544100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13825400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13019200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10300200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7342800</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1280,9 +1337,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1310,9 +1370,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1340,9 +1403,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1370,69 +1436,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>1437700</v>
+      </c>
+      <c r="E32" s="3">
         <v>1376100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1328900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1123600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9487600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2054800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1031500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>928900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>840400</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>11391600</v>
+      </c>
+      <c r="E33" s="3">
         <v>12010900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13311400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10025200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>18544100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13825400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13019200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10300200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7342800</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1460,74 +1535,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>11391600</v>
+      </c>
+      <c r="E35" s="3">
         <v>12010900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13311400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10025200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>18544100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13825400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13019200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10300200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7342800</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1540,8 +1624,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1554,278 +1639,306 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>5774600</v>
+      </c>
+      <c r="E41" s="3">
         <v>6131200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5719300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5960000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7665600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5916900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7712000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4573400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8145200</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>2082100</v>
+      </c>
+      <c r="E42" s="3">
         <v>2554700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1229100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1333400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7733600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3922000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2943800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5952500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>828100</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>15062700</v>
+      </c>
+      <c r="E43" s="3">
         <v>13888000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>14582100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>13411300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>13557300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12946000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12941800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12232200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13291100</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>16158600</v>
+      </c>
+      <c r="E44" s="3">
         <v>14632900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14127300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16242600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>13143800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>11416800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9647000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9273800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9416600</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>634300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1025200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>368100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>377400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>332400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3764900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3064600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9101000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>447400</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>40316500</v>
+      </c>
+      <c r="E46" s="3">
         <v>38831100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>36644700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37918400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>43063400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>38505800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36823300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>41671400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>32716300</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>19846100</v>
+      </c>
+      <c r="E47" s="3">
         <v>19837100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>19042600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>17602000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>16048500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>16500700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14575300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>13576800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>18091200</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>41048000</v>
+      </c>
+      <c r="E48" s="3">
         <v>37195700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36181500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32596500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31093300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29206000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>29697800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>30444300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31580400</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>55878700</v>
+      </c>
+      <c r="E49" s="3">
         <v>55000100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>55718100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>55694500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>58396700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>53990400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>48240000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>51156600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>51675600</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1853,9 +1966,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -1883,39 +1999,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>2069500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1720400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1296800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1255600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2651400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>529000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>583400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>553900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>465900</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -1943,39 +2065,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>160351900</v>
+      </c>
+      <c r="E54" s="3">
         <v>153682500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>150286200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>146194900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>152633300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>140184200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>132102600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>139248500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>136687300</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -1988,8 +2116,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2002,188 +2131,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>20300100</v>
+      </c>
+      <c r="E57" s="3">
         <v>18412500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16857500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17085000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17140000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15599900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14473000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13257700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13226500</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>14636500</v>
+      </c>
+      <c r="E58" s="3">
         <v>13091200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11182100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11779300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11420500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13686400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14791100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>15228300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11850500</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>7443100</v>
+      </c>
+      <c r="E59" s="3">
         <v>7898000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7951900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6927900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7745600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7853100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7104900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9138600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7356100</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>51319800</v>
+      </c>
+      <c r="E60" s="3">
         <v>47300800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>44039600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>43232700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>43900400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>44896300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>42969000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43731500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>39185900</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>58321500</v>
+      </c>
+      <c r="E61" s="3">
         <v>57049400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>54420100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>46957300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>40019300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31566000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23884600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>26118900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>19050600</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1639400</v>
+      </c>
+      <c r="E62" s="3">
         <v>1782200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1959500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2637700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1469900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2384900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1642800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1446200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3717600</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2211,9 +2359,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2241,9 +2392,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2271,39 +2425,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>118662000</v>
+      </c>
+      <c r="E66" s="3">
         <v>113190500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>107074300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>99916700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>93696900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>87611200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>77520700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>79893500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>72833900</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2316,8 +2476,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -2345,9 +2506,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -2375,9 +2539,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -2405,9 +2572,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -2435,39 +2605,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>80145000</v>
+      </c>
+      <c r="E72" s="3">
         <v>73233800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>81064300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>80712000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>89252000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>86817700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>85762400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>85999400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>85812100</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -2495,9 +2671,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -2525,9 +2704,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -2555,39 +2737,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>41377100</v>
+      </c>
+      <c r="E76" s="3">
         <v>39635600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>42445900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>45402100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>58292500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>51647400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>53728000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>58298100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>62547200</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -2615,74 +2803,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>11391600</v>
+      </c>
+      <c r="E81" s="3">
         <v>12010900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13311400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10025200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>18544100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13825400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13019200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10300200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7342800</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -2695,38 +2892,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>4104900</v>
+      </c>
+      <c r="E83" s="3">
         <v>3432000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3554400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3349300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3352300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3534300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3601500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3662800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3652900</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -2754,9 +2955,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -2784,9 +2988,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -2814,9 +3021,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -2844,9 +3054,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -2874,39 +3087,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>20056800</v>
+      </c>
+      <c r="E89" s="3">
         <v>18401400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18931000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12877000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>15208300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>16249800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>16365700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>15649000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>14569700</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -2919,38 +3138,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-5709100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6221700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6785700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5510100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5353200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4607000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3815200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3932100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4040800</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -2978,9 +3201,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3008,39 +3234,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-5507300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9516900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7358100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2058000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3339100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6405200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>8627900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14498600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5079200</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3053,38 +3285,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>9898500</v>
+      </c>
+      <c r="E96" s="3">
         <v>8625200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>9297400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>8238600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>8425800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>8703000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>7465200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>7240100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>7312000</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -3112,9 +3348,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -3142,9 +3381,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -3172,97 +3414,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-15215300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8124200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-11588200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12312500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10039400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11734400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21844300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4184100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9321100</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-548600</v>
+      </c>
+      <c r="E101" s="3">
         <v>58500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-809900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-108100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>97600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-635200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-228200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-318100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-222700</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-1214500</v>
+      </c>
+      <c r="E102" s="3">
         <v>818800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-825400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1601700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1927400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2525000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2921000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3351800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-53400</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
